--- a/artfynd/A 13261-2021 artfynd.xlsx
+++ b/artfynd/A 13261-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13261-2021 artfynd.xlsx
+++ b/artfynd/A 13261-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91475863</v>
+        <v>97474493</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
+        <v>90676</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Iggön, Ö kanten av ängen N Myrorna, mellan ladorna, Gstr</t>
+          <t>Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625619.4944896537</v>
+        <v>625546.4598672757</v>
       </c>
       <c r="R2" t="n">
-        <v>6751054.508785872</v>
+        <v>6751007.578651917</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1993-06-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1993-06-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -772,144 +772,18 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>V-exponerad torrängsbacke mellan äng och skogsbryn</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 70329N</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>97474493</v>
-      </c>
-      <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Iggön, Gstr</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>625546.4598672757</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6751007.578651917</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Gävle</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hille</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
